--- a/sources/paul_step8c.xlsx
+++ b/sources/paul_step8c.xlsx
@@ -6106,11 +6106,6 @@
           <t>GB MS KNDc</t>
         </is>
       </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="Z69" t="inlineStr">
         <is>
           <t>4c7261dc-3b08-4f73-bfdf-3a3fd2f40faf</t>
@@ -6213,11 +6208,6 @@
           <t>RC</t>
         </is>
       </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="Z70" t="inlineStr">
         <is>
           <t>29b9b04b-f75d-47fa-a2ff-61b4edc23611</t>
@@ -6313,11 +6303,6 @@
       <c r="X71" t="inlineStr">
         <is>
           <t>If delayed the damage is 19 from full crouch and 21 damage starting with the sway.</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">

--- a/sources/paul_step8c.xlsx
+++ b/sources/paul_step8c.xlsx
@@ -996,6 +996,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>1bddff50-c0df-40c7-9efa-29b264583940</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>1bddff50-c0df-40c7-9efa-29b264583940</t>
@@ -1048,6 +1053,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>39dff7b9-ce44-4948-ad1f-b1ef695ca9a3</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>39dff7b9-ce44-4948-ad1f-b1ef695ca9a3</t>
@@ -1105,6 +1115,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>701e73a5-cb4f-442c-95a1-4a3d33f87d73</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>701e73a5-cb4f-442c-95a1-4a3d33f87d73</t>
@@ -1162,6 +1177,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>0837c7ed-0764-4f99-a630-8ac829f5cd48</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>0837c7ed-0764-4f99-a630-8ac829f5cd48</t>
@@ -1219,6 +1239,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>8f4adaf4-8d96-4db4-9e5d-c30c5a7019be</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>8f4adaf4-8d96-4db4-9e5d-c30c5a7019be</t>
@@ -1276,6 +1301,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>9ceaa1aa-aa76-418f-a422-c4dcb6b6e146</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>9ceaa1aa-aa76-418f-a422-c4dcb6b6e146</t>
@@ -1333,6 +1363,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>b7497a64-e28b-4906-90d2-9ce8f800b5db</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>b7497a64-e28b-4906-90d2-9ce8f800b5db</t>
@@ -1400,6 +1435,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>298a11b7-cb2d-4207-89d4-785146ac1d79</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>298a11b7-cb2d-4207-89d4-785146ac1d79</t>
@@ -1462,6 +1502,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>f4807f21-048f-4fcc-be89-b4ed5bad669d</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>f4807f21-048f-4fcc-be89-b4ed5bad669d</t>
@@ -1522,6 +1567,11 @@
       <c r="V17" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>714cac8f-98de-4f0c-bfac-510c28ebaccd</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -7995,6 +8045,11 @@
           <t>hhmmlmhmLm</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>8b2ab344-e968-4445-b403-e548e2f0db2d</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>8b2ab344-e968-4445-b403-e548e2f0db2d</t>
@@ -8042,6 +8097,11 @@
           <t>hhmhmhhlmm</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>9c058e2e-80b5-4da3-b171-a802077dec24</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>9c058e2e-80b5-4da3-b171-a802077dec24</t>
@@ -8087,6 +8147,11 @@
       <c r="T94" t="inlineStr">
         <is>
           <t>hhmmm</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>e1a2f47f-32a9-46a1-bc65-d50cded77733</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">

--- a/sources/paul_step8c.xlsx
+++ b/sources/paul_step8c.xlsx
@@ -417,38 +417,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC94"/>
+  <dimension ref="A1:AD94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col hidden="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col hidden="1" min="5" max="5"/>
-    <col width="51" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col hidden="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col hidden="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col hidden="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col hidden="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
-    <col hidden="1" min="17" max="17"/>
-    <col width="25" customWidth="1" min="18" max="18"/>
-    <col hidden="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col hidden="1" min="6" max="6"/>
+    <col width="51" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col hidden="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col hidden="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col hidden="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col hidden="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="25" customWidth="1" min="17" max="17"/>
+    <col hidden="1" min="18" max="18"/>
+    <col width="25" customWidth="1" min="19" max="19"/>
+    <col hidden="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="84" customWidth="1" min="24" max="24"/>
-    <col width="10" customWidth="1" min="25" max="25"/>
-    <col width="38" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="84" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="26" max="26"/>
     <col width="38" customWidth="1" min="27" max="27"/>
     <col width="38" customWidth="1" min="28" max="28"/>
-    <col width="11" customWidth="1" min="29" max="29"/>
+    <col width="38" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -481,125 +482,130 @@
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q2" s="1" t="inlineStr">
+      <c r="R2" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="R2" s="1" t="inlineStr">
+      <c r="S2" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="S2" s="1" t="inlineStr">
+      <c r="T2" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="T2" s="1" t="inlineStr">
+      <c r="U2" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="U2" s="1" t="inlineStr">
+      <c r="V2" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="V2" s="1" t="inlineStr">
+      <c r="W2" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="W2" s="1" t="inlineStr">
+      <c r="X2" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="X2" s="1" t="inlineStr">
+      <c r="Y2" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr">
+      <c r="Z2" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="inlineStr">
+      <c r="AA2" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="AB2" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AB2" s="1" t="inlineStr">
+      <c r="AC2" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AC2" s="1" t="inlineStr">
+      <c r="AD2" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -616,57 +622,57 @@
           <t>1+3</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Over the Shoulder</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Over the Shoulder</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>f047c9b0-3722-4bee-b68f-c403b748194f</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>c5690230-14d7-4591-be18-98732f0d9439</t>
         </is>
@@ -683,57 +689,57 @@
           <t>2+4</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Shoulder Pop</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Shoulder Pop</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>7f7989a0-c998-4027-bf31-37608a6c146d</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>99d12cd5-dab9-467d-8b0f-0774f2098538</t>
         </is>
@@ -750,57 +756,57 @@
           <t>b+2+3</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Foot Launch</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Foot Launch</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>0a0aa5d0-7734-4184-8e17-e77497af8fa7</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>8d72dd90-ffe3-4089-ad91-22dfe8b33e75</t>
         </is>
@@ -817,57 +823,57 @@
           <t>df+1+2</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Twist and Shout</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Twist and Shout</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>1+2</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>218cb0c0-a423-4b49-8b83-cc222d388292</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>63e1b031-ab65-4c1d-a38e-dfacfc455adc</t>
         </is>
@@ -884,62 +890,62 @@
           <t>f,f+1+2</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Shoulder Ram</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Shoulder Ram</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>1+2</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>7b7111fd-006e-4ce3-a158-85184388ac06</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>d87918ed-af95-47a7-b73f-e28a2cd470a7</t>
         </is>
@@ -963,50 +969,55 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>db+1+2</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>Ultimate Tackle</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Ultimate Tackle</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>1bddff50-c0df-40c7-9efa-29b264583940</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>1bddff50-c0df-40c7-9efa-29b264583940</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1023,52 +1034,62 @@
           <t>FC+1+2 ,1 ,2 ,1 ,2 ,1</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1,2,1,1,2</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>FC+1+2,1,2,1,1,2</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>– Ultimate Punches</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Ultimate Tackle – Ultimate Punches</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>5,5,5,5,5</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>5,5,5,5,5,5</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>39dff7b9-ce44-4948-ad1f-b1ef695ca9a3</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>39dff7b9-ce44-4948-ad1f-b1ef695ca9a3</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1bddff50-c0df-40c7-9efa-29b264583940</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1085,52 +1106,62 @@
           <t>FC+1+2 ,2 ,1 ,2 ,1 ,2</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2,1,2,2,1</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>FC+1+2,2,1,2,2,1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>– Ultimate Punches</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Ultimate Tackle – Ultimate Punches</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>5,5,5,5,5</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>5,5,5,5,5,5</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>701e73a5-cb4f-442c-95a1-4a3d33f87d73</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>701e73a5-cb4f-442c-95a1-4a3d33f87d73</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1bddff50-c0df-40c7-9efa-29b264583940</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1147,52 +1178,52 @@
           <t>FC+1+2 ,1 ,2 ,1 ,1+2</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>– Punches - Cross Arm Lock</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Ultimate Tackle – Punches - Cross Arm Lock</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>5,5,5,25</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>5,5,5,5,25</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>0837c7ed-0764-4f99-a630-8ac829f5cd48</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>0837c7ed-0764-4f99-a630-8ac829f5cd48</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1bddff50-c0df-40c7-9efa-29b264583940</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1209,52 +1240,52 @@
           <t>FC+1+2 ,2 ,1 ,2 ,1+2</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>– Punches - Cross Arm Lock</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Ultimate Tackle – Punches - Cross Arm Lock</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>5,5,5,25</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>5,5,5,5,25</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>8f4adaf4-8d96-4db4-9e5d-c30c5a7019be</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>8f4adaf4-8d96-4db4-9e5d-c30c5a7019be</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1bddff50-c0df-40c7-9efa-29b264583940</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1271,52 +1302,52 @@
           <t>FC+1+2 ,1+2</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>– Cross Arm Lock</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Ultimate Tackle – Cross Arm Lock</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>5,25</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>9ceaa1aa-aa76-418f-a422-c4dcb6b6e146</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>9ceaa1aa-aa76-418f-a422-c4dcb6b6e146</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>1bddff50-c0df-40c7-9efa-29b264583940</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1333,52 +1364,52 @@
           <t>FC+1+2 ,2 ,D+1 ,1,N ,4 ,1 ,1+2</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>– Ultimate Punishment</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Ultimate Tackle – Ultimate Punishment</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>5,8,8,35</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>5,5,8,8,35</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>b7497a64-e28b-4906-90d2-9ce8f800b5db</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>b7497a64-e28b-4906-90d2-9ce8f800b5db</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>1bddff50-c0df-40c7-9efa-29b264583940</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1402,50 +1433,55 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>Dragon Screw</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Dragon Screw</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>298a11b7-cb2d-4207-89d4-785146ac1d79</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>298a11b7-cb2d-4207-89d4-785146ac1d79</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1469,50 +1505,55 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>Fall Away</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Fall Away</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>f4807f21-048f-4fcc-be89-b4ed5bad669d</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>f4807f21-048f-4fcc-be89-b4ed5bad669d</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1536,50 +1577,55 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>Reverse Neck Throw</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Reverse Neck Throw</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Back</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>714cac8f-98de-4f0c-bfac-510c28ebaccd</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>714cac8f-98de-4f0c-bfac-510c28ebaccd</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1616,125 +1662,130 @@
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F20" s="1" t="inlineStr">
+      <c r="G20" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G20" s="1" t="inlineStr">
+      <c r="H20" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H20" s="1" t="inlineStr">
+      <c r="I20" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="I20" s="1" t="inlineStr">
+      <c r="J20" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="J20" s="1" t="inlineStr">
+      <c r="K20" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="K20" s="1" t="inlineStr">
+      <c r="L20" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="L20" s="1" t="inlineStr">
+      <c r="M20" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="M20" s="1" t="inlineStr">
+      <c r="N20" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="N20" s="1" t="inlineStr">
+      <c r="O20" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="O20" s="1" t="inlineStr">
+      <c r="P20" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="P20" s="1" t="inlineStr">
+      <c r="Q20" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q20" s="1" t="inlineStr">
+      <c r="R20" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="R20" s="1" t="inlineStr">
+      <c r="S20" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="S20" s="1" t="inlineStr">
+      <c r="T20" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="T20" s="1" t="inlineStr">
+      <c r="U20" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="U20" s="1" t="inlineStr">
+      <c r="V20" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="V20" s="1" t="inlineStr">
+      <c r="W20" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="W20" s="1" t="inlineStr">
+      <c r="X20" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="X20" s="1" t="inlineStr">
+      <c r="Y20" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Y20" s="1" t="inlineStr">
+      <c r="Z20" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Z20" s="1" t="inlineStr">
+      <c r="AA20" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AA20" s="1" t="inlineStr">
+      <c r="AB20" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AB20" s="1" t="inlineStr">
+      <c r="AC20" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AC20" s="1" t="inlineStr">
+      <c r="AD20" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -1751,77 +1802,77 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>2751baf5-415a-46a0-92a4-ad07ef794525</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>6f25966e-3ba0-4aa1-b7ed-b89bde2b8b88</t>
         </is>
@@ -1838,77 +1889,77 @@
           <t>2</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>1afeb3ed-8f0b-41e9-863c-b37a22eeaa62</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>a2db9f5d-05da-4ef2-ac95-ddff36b94d51</t>
         </is>
@@ -1925,77 +1976,77 @@
           <t>3</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>5d3d9115-095e-453d-a753-7fd7348de5b4</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>df22d70b-aa8d-4f3f-9af0-d00ed762d498</t>
         </is>
@@ -2012,77 +2063,77 @@
           <t>4</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>39f76a6f-d6f0-4947-be9b-62f8233c96eb</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>24d90bd4-59de-45bb-8b61-63a2d9faf138</t>
         </is>
@@ -2099,77 +2150,77 @@
           <t>f+1</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>a34e583f-69f1-4600-91cd-d870c7b2b7a7</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>0f64d5d7-9f71-4794-b10e-60e851d1f858</t>
         </is>
@@ -2186,77 +2237,77 @@
           <t>f+2</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>4e521fa4-98b2-4320-a49b-4267f40fb897</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>750ed946-fd17-4bbb-9dcb-6181bd8590e4</t>
         </is>
@@ -2273,77 +2324,77 @@
           <t>f+3</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>bfbec491-c548-46ea-8271-c9bdb442d873</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>2ec09e78-a70f-45d6-89a8-e176ed4d7e4c</t>
         </is>
@@ -2360,77 +2411,77 @@
           <t>f+4</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>dcc2b9b6-6a1b-452b-b48f-e13f6ff937f2</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>9e428146-8d63-460b-8c74-731c7abe0273</t>
         </is>
@@ -2447,77 +2498,77 @@
           <t>d+1</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>9c7dc016-5b47-4eb3-b2c0-495d5b13355e</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>cc8b99b6-99e4-441c-acfd-b2bc9a7a3bd8</t>
         </is>
@@ -2534,77 +2585,77 @@
           <t>d+2</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>90ab6654-86ac-4f44-a39f-5725d4d13ecd</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>7656bf5e-8413-463c-b5c9-a0f93965b5be</t>
         </is>
@@ -2621,77 +2672,77 @@
           <t>d+3</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>e5b3e4ae-1349-4f0c-8563-1c678d9840fe</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>8296b824-0163-41e4-8fb6-b805b9407f94</t>
         </is>
@@ -2708,77 +2759,77 @@
           <t>d+4</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>-34</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>-34</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>e99f7fc8-b502-4978-9219-8d3a9ec84c3e</t>
         </is>
       </c>
-      <c r="AA32" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>0273a63a-5257-4a2f-a1f9-2725d8791a51</t>
         </is>
@@ -2795,77 +2846,77 @@
           <t>FC+1</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>dde090e7-74ed-416d-85a8-46179c38c9e6</t>
         </is>
       </c>
-      <c r="AA33" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>06d34668-d183-4479-914c-df2d4bf65e6c</t>
         </is>
@@ -2882,77 +2933,77 @@
           <t>FC+2</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>3546ab20-5637-4ded-a027-f28f254c0b1f</t>
         </is>
       </c>
-      <c r="AA34" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>d58cdedb-1726-43a3-9bde-95f929295484</t>
         </is>
@@ -2969,77 +3020,77 @@
           <t>FC+3</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>9b480a3a-d06d-4082-ba06-1bc3804585d2</t>
         </is>
       </c>
-      <c r="AA35" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>ae1e82f5-fc0e-4a39-bafb-0cc1b99fe3ee</t>
         </is>
@@ -3056,77 +3107,77 @@
           <t>FC+4</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>eb0e0efc-a02c-42e4-8059-2b801a7bda39</t>
         </is>
       </c>
-      <c r="AA36" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>7af0b56f-100e-443b-8998-27681ceecff6</t>
         </is>
@@ -3143,77 +3194,77 @@
           <t>WS+1</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>039a9afa-c198-49ad-b175-4f14fe8e66b6</t>
         </is>
       </c>
-      <c r="AA37" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>6f4a6224-d964-4d61-9899-6ed5279c8425</t>
         </is>
@@ -3230,77 +3281,77 @@
           <t>WS+2</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>-18</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>-18</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="R38" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
+      <c r="AA38" t="inlineStr">
         <is>
           <t>ba27fce5-4145-4046-a58f-74588494dd3c</t>
         </is>
       </c>
-      <c r="AA38" t="inlineStr">
+      <c r="AB38" t="inlineStr">
         <is>
           <t>5ed4377f-58b1-4a06-ae12-430e680d0b63</t>
         </is>
@@ -3317,77 +3368,77 @@
           <t>WS+3</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="R39" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
+      <c r="AA39" t="inlineStr">
         <is>
           <t>ba7bf57e-3b3a-4c5d-bbe0-81c3210b0d09</t>
         </is>
       </c>
-      <c r="AA39" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>bc99ac15-ecad-4d82-8f27-7eaa78d5ece3</t>
         </is>
@@ -3404,77 +3455,77 @@
           <t>WS+4</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>6f93d1f7-77be-43f4-9c3c-579965bcfce4</t>
         </is>
       </c>
-      <c r="AA40" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>3fef6716-3245-4a89-a5d2-da1462679d15</t>
         </is>
@@ -3491,77 +3542,77 @@
           <t>df+1</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>78504860-5f2a-46fc-bd09-17b55819f476</t>
         </is>
       </c>
-      <c r="AA41" t="inlineStr">
+      <c r="AB41" t="inlineStr">
         <is>
           <t>6526bd69-cfc4-4fab-b821-7121b25ade06</t>
         </is>
@@ -3578,77 +3629,77 @@
           <t>df+2</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="AA42" t="inlineStr">
         <is>
           <t>b402c235-8f6d-4f10-8026-ba5e01b106d4</t>
         </is>
       </c>
-      <c r="AA42" t="inlineStr">
+      <c r="AB42" t="inlineStr">
         <is>
           <t>0f46a245-7a24-47dc-93f6-af841b56448b</t>
         </is>
@@ -3665,77 +3716,77 @@
           <t>df+3</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
+      <c r="AA43" t="inlineStr">
         <is>
           <t>fda9075c-1e74-4a54-acbe-270ffd661a56</t>
         </is>
       </c>
-      <c r="AA43" t="inlineStr">
+      <c r="AB43" t="inlineStr">
         <is>
           <t>e1036115-ced3-43a5-be85-14eb98659491</t>
         </is>
@@ -3752,77 +3803,77 @@
           <t>df+4</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
+      <c r="AA44" t="inlineStr">
         <is>
           <t>fe2daa15-f92a-4ded-ad89-d35941e1a383</t>
         </is>
       </c>
-      <c r="AA44" t="inlineStr">
+      <c r="AB44" t="inlineStr">
         <is>
           <t>e60300c6-61d8-4058-95db-20237f485f13</t>
         </is>
@@ -3859,125 +3910,130 @@
       </c>
       <c r="E47" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F47" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F47" s="1" t="inlineStr">
+      <c r="G47" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G47" s="1" t="inlineStr">
+      <c r="H47" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H47" s="1" t="inlineStr">
+      <c r="I47" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="I47" s="1" t="inlineStr">
+      <c r="J47" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="J47" s="1" t="inlineStr">
+      <c r="K47" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="K47" s="1" t="inlineStr">
+      <c r="L47" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="L47" s="1" t="inlineStr">
+      <c r="M47" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="M47" s="1" t="inlineStr">
+      <c r="N47" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="N47" s="1" t="inlineStr">
+      <c r="O47" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="O47" s="1" t="inlineStr">
+      <c r="P47" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="P47" s="1" t="inlineStr">
+      <c r="Q47" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q47" s="1" t="inlineStr">
+      <c r="R47" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="R47" s="1" t="inlineStr">
+      <c r="S47" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="S47" s="1" t="inlineStr">
+      <c r="T47" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="T47" s="1" t="inlineStr">
+      <c r="U47" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="U47" s="1" t="inlineStr">
+      <c r="V47" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="V47" s="1" t="inlineStr">
+      <c r="W47" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="W47" s="1" t="inlineStr">
+      <c r="X47" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="X47" s="1" t="inlineStr">
+      <c r="Y47" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Y47" s="1" t="inlineStr">
+      <c r="Z47" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Z47" s="1" t="inlineStr">
+      <c r="AA47" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AA47" s="1" t="inlineStr">
+      <c r="AB47" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AB47" s="1" t="inlineStr">
+      <c r="AC47" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AC47" s="1" t="inlineStr">
+      <c r="AD47" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -3994,87 +4050,87 @@
           <t>1 ,2</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Double Punch</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>Double Punch</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>+2 0</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>+2 0</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>+5 +6</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>+5 +6</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>+5 +6</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>+5 +6</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>5,15</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>5,15</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
+      <c r="AA48" t="inlineStr">
         <is>
           <t>5fbd609f-714d-454d-b251-80c1229ec45c</t>
         </is>
       </c>
-      <c r="AA48" t="inlineStr">
+      <c r="AB48" t="inlineStr">
         <is>
           <t>0ed86bfa-e761-43af-98e3-320f11762d5b</t>
         </is>
@@ -4091,92 +4147,92 @@
           <t>1 ,4</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Reverse PDK Combo</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>Reverse PDK Combo</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>+2 -10</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>+2 -10</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>+5 +1</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>+5 +1</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>+5 +1</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>+5 +1</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>5,8</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>5,8</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>hl</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>hl</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
+      <c r="AA49" t="inlineStr">
         <is>
           <t>b0ba5867-cbef-4d6e-aa6b-d2b092e2a3f1</t>
         </is>
       </c>
-      <c r="AA49" t="inlineStr">
+      <c r="AB49" t="inlineStr">
         <is>
           <t>6e2cdb8f-0974-4bbe-bd0d-cd265dd3d488</t>
         </is>
@@ -4193,92 +4249,92 @@
           <t>f+1+2</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Hammer of Gods</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>Hammer of Gods</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>GB SLDc KSco</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
+      <c r="AA50" t="inlineStr">
         <is>
           <t>fffda5eb-facf-4657-9fc0-ecadc45eaa29</t>
         </is>
       </c>
-      <c r="AA50" t="inlineStr">
+      <c r="AB50" t="inlineStr">
         <is>
           <t>b803f236-19d0-4a62-a106-d1d418a84d41</t>
         </is>
@@ -4295,87 +4351,87 @@
           <t>f+1+4</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Shoulder Rush</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Shoulder Rush</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>-19</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>-19</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
+      <c r="AA51" t="inlineStr">
         <is>
           <t>6c834ef1-a885-4b01-8f88-f6454299b1d2</t>
         </is>
       </c>
-      <c r="AA51" t="inlineStr">
+      <c r="AB51" t="inlineStr">
         <is>
           <t>112cbaec-a52d-4329-be01-342d92d57f2f</t>
         </is>
@@ -4392,102 +4448,102 @@
           <t>qcf+1</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Thruster</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>Thruster</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="R52" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>JG FSc</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
+      <c r="Y52" t="inlineStr">
         <is>
           <t>If a tag is buffered the move will juggle even on a counter hit.</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
+      <c r="AA52" t="inlineStr">
         <is>
           <t>d8ca6879-38de-4b7a-b2ec-ed8aa865dbfa</t>
         </is>
       </c>
-      <c r="AA52" t="inlineStr">
+      <c r="AB52" t="inlineStr">
         <is>
           <t>c9e9e10f-dfbe-480b-b969-1fd1387673ae</t>
         </is>
@@ -4504,87 +4560,87 @@
           <t>d+1</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Tile Splitter</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>Tile Splitter</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="R53" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="U53" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
+      <c r="AA53" t="inlineStr">
         <is>
           <t>3dc45548-0f0e-41e3-8ac9-3700ef44baf0</t>
         </is>
       </c>
-      <c r="AA53" t="inlineStr">
+      <c r="AB53" t="inlineStr">
         <is>
           <t>8919b48f-b469-45eb-9706-c500d5097715</t>
         </is>
@@ -4601,87 +4657,87 @@
           <t>d+1 ,2</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>– Deathfist</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>Tile Splitter – Deathfist</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>-8 -17</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>-8 KD</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>+4 KD</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="R54" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>15,26</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="U54" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
+      <c r="AA54" t="inlineStr">
         <is>
           <t>6b3749da-6237-4893-ae65-ba3d73130f40</t>
         </is>
       </c>
-      <c r="AA54" t="inlineStr">
+      <c r="AB54" t="inlineStr">
         <is>
           <t>5ce9c3e1-fc7b-4fd6-af89-7715b1971edd</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
+      <c r="AC54" t="inlineStr">
         <is>
           <t>3dc45548-0f0e-41e3-8ac9-3700ef44baf0</t>
         </is>
@@ -4698,87 +4754,87 @@
           <t>d+1 ,4 ,2</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>– Falling Leaf</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>Tile Splitter – Falling Leaf</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>-34 -17</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>-8 -34 -17</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>-8 KD KD</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>+4 KD KD</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>15,21</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="R55" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>15,15,21</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>lm</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="U55" t="inlineStr">
         <is>
           <t>mlm</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
+      <c r="AA55" t="inlineStr">
         <is>
           <t>7214bc93-737f-4104-815a-ec4462bb3faa</t>
         </is>
       </c>
-      <c r="AA55" t="inlineStr">
+      <c r="AB55" t="inlineStr">
         <is>
           <t>0a31c965-f241-4ff0-85aa-bc0008afc22c</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
+      <c r="AC55" t="inlineStr">
         <is>
           <t>3dc45548-0f0e-41e3-8ac9-3700ef44baf0</t>
         </is>
@@ -4795,92 +4851,92 @@
           <t>SS+1</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Turn Thruster</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>Turn Thruster</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="R56" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="U56" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="W56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>GB KNDc</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
+      <c r="AA56" t="inlineStr">
         <is>
           <t>7f4d2bb5-86b1-432f-86b3-bc063b1974f2</t>
         </is>
       </c>
-      <c r="AA56" t="inlineStr">
+      <c r="AB56" t="inlineStr">
         <is>
           <t>c4506563-ee5d-4d03-8450-5bbe6acdd470</t>
         </is>
@@ -4897,87 +4953,87 @@
           <t>2 ,3</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>PK Combo</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>PK Combo</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>0 -12</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>0 -12</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>+6 KD</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>+6 KD</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>+6 KD</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>+6 KD</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>12,21</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="R57" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>12,21</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
+      <c r="AA57" t="inlineStr">
         <is>
           <t>5574a2a6-09b5-4848-a625-955bed69117a</t>
         </is>
       </c>
-      <c r="AA57" t="inlineStr">
+      <c r="AB57" t="inlineStr">
         <is>
           <t>b1643a4c-93b5-4f58-9309-0977adf9fd82</t>
         </is>
@@ -4994,92 +5050,92 @@
           <t>2 ,d+3</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>PDK Combo</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>PDK Combo</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>0 -15</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>0 -15</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>+6 -1</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>+6 -1</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>+6 -1</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>+6 -1</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>12,8</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="R58" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>12,8</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>hL</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="U58" t="inlineStr">
         <is>
           <t>hL</t>
         </is>
       </c>
-      <c r="W58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
+      <c r="AA58" t="inlineStr">
         <is>
           <t>78bb506b-a510-4c11-a6df-2f94797693e6</t>
         </is>
       </c>
-      <c r="AA58" t="inlineStr">
+      <c r="AB58" t="inlineStr">
         <is>
           <t>8b07e38a-06d7-465f-87ae-63f3d3b66c79</t>
         </is>
@@ -5096,87 +5152,87 @@
           <t>f+2 ,3</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>Quick PK Combo</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>Quick PK Combo</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>0 -26</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>0 -26</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>+6 -12</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>+6 -12</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>+6 -12</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>+6 -12</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>12,20</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="R59" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>12,20</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="T59" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="U59" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
+      <c r="AA59" t="inlineStr">
         <is>
           <t>a4e0d9bd-f0f9-42fe-81a7-454c1b302250</t>
         </is>
       </c>
-      <c r="AA59" t="inlineStr">
+      <c r="AB59" t="inlineStr">
         <is>
           <t>1f08d52e-6230-4b01-8c83-1000f672782d</t>
         </is>
@@ -5193,87 +5249,87 @@
           <t>f,f+2</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>Flash Elbow</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>Flash Elbow</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>-18</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>-18</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="R60" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="U60" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
+      <c r="AA60" t="inlineStr">
         <is>
           <t>19bad066-be7c-437f-88c7-b5ac221fb4c7</t>
         </is>
       </c>
-      <c r="AA60" t="inlineStr">
+      <c r="AB60" t="inlineStr">
         <is>
           <t>c6121bb5-f033-4d36-a8d8-71ba5a4ce028</t>
         </is>
@@ -5290,92 +5346,92 @@
           <t>df+2</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Upper</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>Upper</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="R61" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="U61" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
+      <c r="AA61" t="inlineStr">
         <is>
           <t>1853ae5c-ff75-4759-8c17-d8e945634bb4</t>
         </is>
       </c>
-      <c r="AA61" t="inlineStr">
+      <c r="AB61" t="inlineStr">
         <is>
           <t>e807c91c-1dab-486e-8900-1a9c90d1a5a8</t>
         </is>
@@ -5392,92 +5448,92 @@
           <t>qcf+2</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>Death Fist</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>Death Fist</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="R62" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="T62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr">
+      <c r="U62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="Y62" t="inlineStr">
         <is>
           <t>Damage is 49 on a clean hit.</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
+      <c r="AA62" t="inlineStr">
         <is>
           <t>8b652985-e651-40f1-bd83-a78b7bb52cac</t>
         </is>
       </c>
-      <c r="AA62" t="inlineStr">
+      <c r="AB62" t="inlineStr">
         <is>
           <t>2298e750-7114-4b3d-b913-e3a78dddd1d2</t>
         </is>
@@ -5494,92 +5550,92 @@
           <t>WS+2</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>Thunder Palm</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>Thunder Palm</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>-18</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>-18</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="R63" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="T63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr">
+      <c r="U63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
+      <c r="AA63" t="inlineStr">
         <is>
           <t>245528bf-14fb-4c46-a13e-0dd7a99e473a</t>
         </is>
       </c>
-      <c r="AA63" t="inlineStr">
+      <c r="AB63" t="inlineStr">
         <is>
           <t>3aeda0b1-d653-440b-871f-404448526edb</t>
         </is>
@@ -5603,85 +5659,90 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
+          <t>DF+2</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t>Jaw Breaker</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>Jaw Breaker</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>-19</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>-19</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="R64" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="T64" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr">
+      <c r="U64" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
+      <c r="AA64" t="inlineStr">
         <is>
           <t>07feabb0-e611-41d7-bf33-7295d9aa9c08</t>
         </is>
       </c>
-      <c r="AA64" t="inlineStr">
+      <c r="AB64" t="inlineStr">
         <is>
           <t>3cd515ca-d0f4-4f48-b97a-26b779c252e1</t>
         </is>
@@ -5698,92 +5759,92 @@
           <t>FC+df+2 &lt;1</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>– Gut Buster</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>Jaw Breaker – Gut Buster</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>-19 -17</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>-6 KD</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>-6 KD</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="R65" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>21,25</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="T65" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr">
+      <c r="U65" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
+      <c r="Y65" t="inlineStr">
         <is>
           <t>If delayed the damage is 19 from full crouch and 21 damage starting with the sway.</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
+      <c r="AA65" t="inlineStr">
         <is>
           <t>cde712c6-d4c6-43bb-8752-afb4969bc0ce</t>
         </is>
       </c>
-      <c r="AA65" t="inlineStr">
+      <c r="AB65" t="inlineStr">
         <is>
           <t>15dd606e-b708-4089-ba1f-335f602b7488</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
+      <c r="AC65" t="inlineStr">
         <is>
           <t>07feabb0-e611-41d7-bf33-7295d9aa9c08</t>
         </is>
@@ -5800,97 +5861,97 @@
           <t>FC+df+2 &lt;2</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>– Stone Breaker</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>Jaw Breaker – Stone Breaker</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>-19</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>-19 -19</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>-6 KD</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>-6 KD</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="R66" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr">
+      <c r="S66" t="inlineStr">
         <is>
           <t>21,21</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
+      <c r="T66" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="T66" t="inlineStr">
+      <c r="U66" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="W66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Y66" t="inlineStr">
+      <c r="Z66" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
+      <c r="AA66" t="inlineStr">
         <is>
           <t>23ccf8ae-007b-4a32-9087-46f821e6fd5f</t>
         </is>
       </c>
-      <c r="AA66" t="inlineStr">
+      <c r="AB66" t="inlineStr">
         <is>
           <t>3d2f0b2e-7baa-4d3b-a0f6-53150cc48b4a</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
+      <c r="AC66" t="inlineStr">
         <is>
           <t>07feabb0-e611-41d7-bf33-7295d9aa9c08</t>
         </is>
@@ -5907,52 +5968,52 @@
           <t>qcb</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Sway -</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>Sway -</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
+      <c r="R67" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="T67" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr">
+      <c r="U67" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y67" t="inlineStr">
+      <c r="Z67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
+      <c r="AA67" t="inlineStr">
         <is>
           <t>beb5f472-ed4b-4234-ab96-182b590e4c51</t>
         </is>
       </c>
-      <c r="AA67" t="inlineStr">
+      <c r="AB67" t="inlineStr">
         <is>
           <t>1268710d-0259-48b0-8cec-fd9c78db2339</t>
         </is>
@@ -5969,102 +6030,102 @@
           <t>qcb,1</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>– Tile Splitter</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>Sway - – Tile Splitter</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="R68" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>-,15</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="T68" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr">
+      <c r="U68" t="inlineStr">
         <is>
           <t>-m</t>
         </is>
       </c>
-      <c r="W68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>BNc</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
+      <c r="Y68" t="inlineStr">
         <is>
           <t>Does not need to bounce juggle to buffer a tag.</t>
         </is>
       </c>
-      <c r="Y68" t="inlineStr">
+      <c r="Z68" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
+      <c r="AA68" t="inlineStr">
         <is>
           <t>fa883520-01fd-4fd5-98ab-d871ed7c7677</t>
         </is>
       </c>
-      <c r="AA68" t="inlineStr">
+      <c r="AB68" t="inlineStr">
         <is>
           <t>ef1ef571-85e9-4c56-a802-df129bb27afa</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
+      <c r="AC68" t="inlineStr">
         <is>
           <t>beb5f472-ed4b-4234-ab96-182b590e4c51</t>
         </is>
@@ -6081,92 +6142,92 @@
           <t>qcb,2</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>– Rubberband Fist</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>Sway - – Rubberband Fist</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr">
+      <c r="P69" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr">
+      <c r="R69" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>-,18</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
+      <c r="T69" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T69" t="inlineStr">
+      <c r="U69" t="inlineStr">
         <is>
           <t>-m</t>
         </is>
       </c>
-      <c r="W69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>GB MS KNDc</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
+      <c r="AA69" t="inlineStr">
         <is>
           <t>4c7261dc-3b08-4f73-bfdf-3a3fd2f40faf</t>
         </is>
       </c>
-      <c r="AA69" t="inlineStr">
+      <c r="AB69" t="inlineStr">
         <is>
           <t>5b11e267-a2a8-4f64-90d5-9dfaeefe47ba</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
+      <c r="AC69" t="inlineStr">
         <is>
           <t>beb5f472-ed4b-4234-ab96-182b590e4c51</t>
         </is>
@@ -6183,92 +6244,92 @@
           <t>qcb,3</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>– Rapid Fire</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>Sway - – Rapid Fire</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>-21</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>-21</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
+      <c r="P70" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="R70" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr">
+      <c r="S70" t="inlineStr">
         <is>
           <t>-,12</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="T70" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="T70" t="inlineStr">
+      <c r="U70" t="inlineStr">
         <is>
           <t>-L</t>
         </is>
       </c>
-      <c r="W70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
+      <c r="AA70" t="inlineStr">
         <is>
           <t>29b9b04b-f75d-47fa-a2ff-61b4edc23611</t>
         </is>
       </c>
-      <c r="AA70" t="inlineStr">
+      <c r="AB70" t="inlineStr">
         <is>
           <t>b4820940-130a-484e-b627-a9a3226bb56b</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
+      <c r="AC70" t="inlineStr">
         <is>
           <t>beb5f472-ed4b-4234-ab96-182b590e4c51</t>
         </is>
@@ -6285,87 +6346,87 @@
           <t>qcb,3 &lt;2 &lt;1</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>–– Jaw Breaker - Gut Buster</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>Sway - – Rapid Fire – Jaw Breaker - Gut Buster</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>-18 -17</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>-21 -18 -17</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>-7 KD</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>-10 -7 KD</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>-7 KD</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
+      <c r="P71" t="inlineStr">
         <is>
           <t>-10 -7 KD</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="Q71" t="inlineStr">
         <is>
           <t>21,25</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
+      <c r="R71" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr">
+      <c r="S71" t="inlineStr">
         <is>
           <t>-,12,21,25</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="T71" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="T71" t="inlineStr">
+      <c r="U71" t="inlineStr">
         <is>
           <t>-Lmm</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
+      <c r="Y71" t="inlineStr">
         <is>
           <t>If delayed the damage is 19 from full crouch and 21 damage starting with the sway.</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
+      <c r="AA71" t="inlineStr">
         <is>
           <t>69e052b7-c29b-4a81-af53-0e7b5c254639</t>
         </is>
       </c>
-      <c r="AA71" t="inlineStr">
+      <c r="AB71" t="inlineStr">
         <is>
           <t>4e7f70de-615e-4e60-b59f-ec73ed95fe77</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
+      <c r="AC71" t="inlineStr">
         <is>
           <t>29b9b04b-f75d-47fa-a2ff-61b4edc23611</t>
         </is>
@@ -6382,92 +6443,92 @@
           <t>qcb,3 &lt;2 &lt;2</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>–– Jaw Breaker - Stone Breaker</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>Sway - – Rapid Fire – Jaw Breaker - Stone Breaker</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>-18 -19</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>-21 -18 -19</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>-7 KD</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>-10 -7 KD</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>-7 KD</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
+      <c r="P72" t="inlineStr">
         <is>
           <t>-10 -7 KD</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="Q72" t="inlineStr">
         <is>
           <t>21,21</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
+      <c r="R72" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr">
+      <c r="S72" t="inlineStr">
         <is>
           <t>-,12,21,21</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
+      <c r="T72" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr">
+      <c r="U72" t="inlineStr">
         <is>
           <t>-LmL</t>
         </is>
       </c>
-      <c r="W72" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Y72" t="inlineStr">
+      <c r="Z72" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
+      <c r="AA72" t="inlineStr">
         <is>
           <t>02f5ae94-2dca-4e0c-8bc9-0f76612a8fe1</t>
         </is>
       </c>
-      <c r="AA72" t="inlineStr">
+      <c r="AB72" t="inlineStr">
         <is>
           <t>7d0d7056-7468-4eab-831a-0491c91e0879</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
+      <c r="AC72" t="inlineStr">
         <is>
           <t>29b9b04b-f75d-47fa-a2ff-61b4edc23611</t>
         </is>
@@ -6484,97 +6545,97 @@
           <t>SS+3</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>Pumpin' Pedal</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>Pumpin' Pedal</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
+      <c r="O73" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr">
+      <c r="P73" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
+      <c r="Q73" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
+      <c r="R73" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr">
+      <c r="S73" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
+      <c r="T73" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="T73" t="inlineStr">
+      <c r="U73" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="W73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>MSc</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
+      <c r="Y73" t="inlineStr">
         <is>
           <t>Damage is 22 on a clean hit.</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
+      <c r="AA73" t="inlineStr">
         <is>
           <t>a955a519-c991-47fc-af4b-4c5d345846a0</t>
         </is>
       </c>
-      <c r="AA73" t="inlineStr">
+      <c r="AB73" t="inlineStr">
         <is>
           <t>20daf80d-0183-4579-ac21-f01a309044eb</t>
         </is>
@@ -6591,87 +6652,87 @@
           <t>uf+3 ,4</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>Shredder</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>Shredder</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>-17 -13</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>-17 -13</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr">
+      <c r="P74" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
+      <c r="Q74" t="inlineStr">
         <is>
           <t>17,22</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr">
+      <c r="R74" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="R74" t="inlineStr">
+      <c r="S74" t="inlineStr">
         <is>
           <t>17,22</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr">
+      <c r="T74" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="T74" t="inlineStr">
+      <c r="U74" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
+      <c r="AA74" t="inlineStr">
         <is>
           <t>aed156a2-b155-487b-b094-72f4909ab4d2</t>
         </is>
       </c>
-      <c r="AA74" t="inlineStr">
+      <c r="AB74" t="inlineStr">
         <is>
           <t>e05655df-a879-4b30-8f06-041e48aefb95</t>
         </is>
@@ -6688,87 +6749,87 @@
           <t>f,f+3 ,4</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Shredder</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>Shredder</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>-7 -13</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>-7 -13</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr">
+      <c r="P75" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t>20,15</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
+      <c r="R75" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr">
+      <c r="S75" t="inlineStr">
         <is>
           <t>20,15</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
+      <c r="T75" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="T75" t="inlineStr">
+      <c r="U75" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
+      <c r="AA75" t="inlineStr">
         <is>
           <t>660adf38-2da5-498f-b0f0-453606cf6b84</t>
         </is>
       </c>
-      <c r="AA75" t="inlineStr">
+      <c r="AB75" t="inlineStr">
         <is>
           <t>c461b39e-5672-4b42-b9f1-c71a71567a4d</t>
         </is>
@@ -6785,92 +6846,92 @@
           <t>f,f+3 ,4 &lt;4</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>– High Kick</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>Shredder – High Kick</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t>-7 -13 -5</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>JD</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t>KD KD JD</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
+      <c r="O76" t="inlineStr">
         <is>
           <t>JD</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr">
+      <c r="P76" t="inlineStr">
         <is>
           <t>KD KD JD</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
+      <c r="Q76" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
+      <c r="R76" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr">
+      <c r="S76" t="inlineStr">
         <is>
           <t>20,15,25</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
+      <c r="T76" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T76" t="inlineStr">
+      <c r="U76" t="inlineStr">
         <is>
           <t>mmh</t>
         </is>
       </c>
-      <c r="W76" t="inlineStr">
+      <c r="X76" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
+      <c r="AA76" t="inlineStr">
         <is>
           <t>901e6a96-f152-4d90-9490-4c23393ad5f6</t>
         </is>
       </c>
-      <c r="AA76" t="inlineStr">
+      <c r="AB76" t="inlineStr">
         <is>
           <t>477e90dc-56e5-42f6-a1da-29c91af5d47b</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
+      <c r="AC76" t="inlineStr">
         <is>
           <t>660adf38-2da5-498f-b0f0-453606cf6b84</t>
         </is>
@@ -6887,87 +6948,87 @@
           <t>f,f+3 ,4 &lt;df+4</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>– Mid Kick</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>Shredder – Mid Kick</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t>-7 -13 -14</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>KD KD -3</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
+      <c r="O77" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr">
+      <c r="P77" t="inlineStr">
         <is>
           <t>KD KD -3</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
+      <c r="Q77" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr">
+      <c r="R77" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr">
+      <c r="S77" t="inlineStr">
         <is>
           <t>20,15,15</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
+      <c r="T77" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T77" t="inlineStr">
+      <c r="U77" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
+      <c r="AA77" t="inlineStr">
         <is>
           <t>0368d97b-e7ae-4884-a604-d51c7013f3df</t>
         </is>
       </c>
-      <c r="AA77" t="inlineStr">
+      <c r="AB77" t="inlineStr">
         <is>
           <t>e96a59ee-0c89-4481-b2ab-c99dd33de81b</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
+      <c r="AC77" t="inlineStr">
         <is>
           <t>660adf38-2da5-498f-b0f0-453606cf6b84</t>
         </is>
@@ -6984,92 +7045,102 @@
           <t>f,f+3 ,4 &lt;d+4</t>
         </is>
       </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>&lt;db+4</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
+          <t>f,f+3,4&lt;db+4</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t>– Low Kick</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>Shredder – Low Kick</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t>-22</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t>-7 -13 -22</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>KD KD -12</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr">
+      <c r="P78" t="inlineStr">
         <is>
           <t>KD KD -12</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr">
+      <c r="Q78" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr">
+      <c r="R78" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr">
+      <c r="S78" t="inlineStr">
         <is>
           <t>20,15,15</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
+      <c r="T78" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="T78" t="inlineStr">
+      <c r="U78" t="inlineStr">
         <is>
           <t>mmL</t>
         </is>
       </c>
-      <c r="W78" t="inlineStr">
+      <c r="X78" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
+      <c r="AA78" t="inlineStr">
         <is>
           <t>1ef3c42b-25c9-494f-9f03-21dab42a2d81</t>
         </is>
       </c>
-      <c r="AA78" t="inlineStr">
+      <c r="AB78" t="inlineStr">
         <is>
           <t>441cb686-22ef-4bba-90cc-f10f17e8de8e</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
+      <c r="AC78" t="inlineStr">
         <is>
           <t>660adf38-2da5-498f-b0f0-453606cf6b84</t>
         </is>
@@ -7086,97 +7157,97 @@
           <t>d+4 ,2</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>Falling Leaf</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>Falling Leaf</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>-31 -29</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t>-31 -29</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>-22 KD</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>-22 KD</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
+      <c r="O79" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr">
+      <c r="P79" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr">
+      <c r="Q79" t="inlineStr">
         <is>
           <t>13,20</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr">
+      <c r="R79" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr">
+      <c r="S79" t="inlineStr">
         <is>
           <t>13,20</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
+      <c r="T79" t="inlineStr">
         <is>
           <t>lm</t>
         </is>
       </c>
-      <c r="T79" t="inlineStr">
+      <c r="U79" t="inlineStr">
         <is>
           <t>lm</t>
         </is>
       </c>
-      <c r="W79" t="inlineStr">
+      <c r="X79" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
       </c>
-      <c r="X79" t="inlineStr">
+      <c r="Y79" t="inlineStr">
         <is>
           <t>On a clean hit the damage is 19 and the opponent is knocked down.</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
+      <c r="AA79" t="inlineStr">
         <is>
           <t>689f7873-4a08-4929-acb1-6086daed8f64</t>
         </is>
       </c>
-      <c r="AA79" t="inlineStr">
+      <c r="AB79" t="inlineStr">
         <is>
           <t>6c9ee1d1-a760-40aa-948f-d3700eb7495a</t>
         </is>
@@ -7193,92 +7264,92 @@
           <t>f,f+4</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>Neutron Bomb</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>Neutron Bomb</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
+      <c r="O80" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr">
+      <c r="P80" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr">
+      <c r="Q80" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr">
+      <c r="R80" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr">
+      <c r="S80" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr">
+      <c r="T80" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T80" t="inlineStr">
+      <c r="U80" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W80" t="inlineStr">
+      <c r="X80" t="inlineStr">
         <is>
           <t>GB JGco RC</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
+      <c r="AA80" t="inlineStr">
         <is>
           <t>01d72688-6d62-407f-8d64-92dada3ff966</t>
         </is>
       </c>
-      <c r="AA80" t="inlineStr">
+      <c r="AB80" t="inlineStr">
         <is>
           <t>c83c8f64-1233-40e3-8c9d-942e2a4b0464</t>
         </is>
@@ -7295,62 +7366,62 @@
           <t>FC+u+2+3+4</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>Incomplete Somersault</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>Incomplete Somersault</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr">
+      <c r="Q81" t="inlineStr">
         <is>
           <t>25 (15 to Paul)</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr">
+      <c r="R81" t="inlineStr">
         <is>
           <t>25 (15 to Paul)</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr">
+      <c r="S81" t="inlineStr">
         <is>
           <t>25 (15 to Paul)</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
+      <c r="T81" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="T81" t="inlineStr">
+      <c r="U81" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
+      <c r="Y81" t="inlineStr">
         <is>
           <t>Stay in full crouch for one second.</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
+      <c r="AA81" t="inlineStr">
         <is>
           <t>9c4cfaf6-6758-47fb-8f4b-bec209c5eef2</t>
         </is>
       </c>
-      <c r="AA81" t="inlineStr">
+      <c r="AB81" t="inlineStr">
         <is>
           <t>f4693e1d-48a0-4b14-931c-6c0ed08e632f</t>
         </is>
@@ -7367,82 +7438,82 @@
           <t>FC+uf+3+4</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>Somersault</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>Somersault</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
+      <c r="O82" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr">
+      <c r="P82" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr">
+      <c r="Q82" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr">
+      <c r="R82" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr">
+      <c r="S82" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
+      <c r="T82" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="T82" t="inlineStr">
+      <c r="U82" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr">
+      <c r="Y82" t="inlineStr">
         <is>
           <t>Only when Law is teamed up with Paul.</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
+      <c r="AA82" t="inlineStr">
         <is>
           <t>e85d4813-0e56-45b8-aa2c-27defe820e74</t>
         </is>
       </c>
-      <c r="AA82" t="inlineStr">
+      <c r="AB82" t="inlineStr">
         <is>
           <t>f4eaf5fb-dc67-426b-adc2-c2959fd0c578</t>
         </is>
@@ -7459,92 +7530,92 @@
           <t>D+2</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>Ground Pounce</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>Ground Pounce</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="N83" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr">
+      <c r="O83" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr">
+      <c r="P83" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr">
+      <c r="Q83" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr">
+      <c r="R83" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr">
+      <c r="S83" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
+      <c r="T83" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="T83" t="inlineStr">
+      <c r="U83" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr">
+      <c r="Y83" t="inlineStr">
         <is>
           <t>Move can only be done when the opponent is knocked of his feet.</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
+      <c r="AA83" t="inlineStr">
         <is>
           <t>94ba69ef-1625-4040-b31b-3df7b7d79956</t>
         </is>
       </c>
-      <c r="AA83" t="inlineStr">
+      <c r="AB83" t="inlineStr">
         <is>
           <t>f28efef5-5e6e-4fc9-a3f7-f31fbda5f6dc</t>
         </is>
@@ -7568,45 +7639,50 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
+          <t>b+2+4</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
           <t>High and Mid Attack Reversal</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>High and Mid Attack Reversal</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr">
+      <c r="Q84" t="inlineStr">
         <is>
           <t>varies</t>
         </is>
       </c>
-      <c r="Q84" t="inlineStr">
+      <c r="R84" t="inlineStr">
         <is>
           <t>varies</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr">
+      <c r="S84" t="inlineStr">
         <is>
           <t>varies</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
+      <c r="T84" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T84" t="inlineStr">
+      <c r="U84" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
+      <c r="AA84" t="inlineStr">
         <is>
           <t>941f6f03-fb22-4909-a775-3b7dde30af3c</t>
         </is>
       </c>
-      <c r="AA84" t="inlineStr">
+      <c r="AB84" t="inlineStr">
         <is>
           <t>f45117d0-92e0-45fb-917a-dfadfa7a0f18</t>
         </is>
@@ -7643,125 +7719,130 @@
       </c>
       <c r="E87" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F87" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F87" s="1" t="inlineStr">
+      <c r="G87" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G87" s="1" t="inlineStr">
+      <c r="H87" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H87" s="1" t="inlineStr">
+      <c r="I87" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="I87" s="1" t="inlineStr">
+      <c r="J87" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="J87" s="1" t="inlineStr">
+      <c r="K87" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="K87" s="1" t="inlineStr">
+      <c r="L87" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="L87" s="1" t="inlineStr">
+      <c r="M87" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="M87" s="1" t="inlineStr">
+      <c r="N87" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="N87" s="1" t="inlineStr">
+      <c r="O87" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="O87" s="1" t="inlineStr">
+      <c r="P87" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="P87" s="1" t="inlineStr">
+      <c r="Q87" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q87" s="1" t="inlineStr">
+      <c r="R87" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="R87" s="1" t="inlineStr">
+      <c r="S87" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="S87" s="1" t="inlineStr">
+      <c r="T87" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="T87" s="1" t="inlineStr">
+      <c r="U87" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="U87" s="1" t="inlineStr">
+      <c r="V87" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="V87" s="1" t="inlineStr">
+      <c r="W87" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="W87" s="1" t="inlineStr">
+      <c r="X87" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="X87" s="1" t="inlineStr">
+      <c r="Y87" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Y87" s="1" t="inlineStr">
+      <c r="Z87" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Z87" s="1" t="inlineStr">
+      <c r="AA87" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AA87" s="1" t="inlineStr">
+      <c r="AB87" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AB87" s="1" t="inlineStr">
+      <c r="AC87" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AC87" s="1" t="inlineStr">
+      <c r="AD87" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -7778,77 +7859,77 @@
           <t>b+1+2</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>Burning Death Fist</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>Burning Death Fist</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr">
+      <c r="N88" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr">
+      <c r="O88" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O88" t="inlineStr">
+      <c r="P88" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr">
+      <c r="Q88" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="Q88" t="inlineStr">
+      <c r="R88" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr">
+      <c r="S88" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="S88" t="inlineStr">
+      <c r="T88" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="T88" t="inlineStr">
+      <c r="U88" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
+      <c r="AA88" t="inlineStr">
         <is>
           <t>31977e61-603e-4ac8-8193-5f8c7afb2320</t>
         </is>
       </c>
-      <c r="AA88" t="inlineStr">
+      <c r="AB88" t="inlineStr">
         <is>
           <t>7e996897-5b1a-4361-aea1-e2263fe194c2</t>
         </is>
@@ -7885,125 +7966,130 @@
       </c>
       <c r="E91" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F91" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F91" s="1" t="inlineStr">
+      <c r="G91" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G91" s="1" t="inlineStr">
+      <c r="H91" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H91" s="1" t="inlineStr">
+      <c r="I91" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="I91" s="1" t="inlineStr">
+      <c r="J91" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="J91" s="1" t="inlineStr">
+      <c r="K91" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="K91" s="1" t="inlineStr">
+      <c r="L91" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="L91" s="1" t="inlineStr">
+      <c r="M91" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="M91" s="1" t="inlineStr">
+      <c r="N91" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="N91" s="1" t="inlineStr">
+      <c r="O91" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="O91" s="1" t="inlineStr">
+      <c r="P91" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="P91" s="1" t="inlineStr">
+      <c r="Q91" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q91" s="1" t="inlineStr">
+      <c r="R91" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="R91" s="1" t="inlineStr">
+      <c r="S91" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="S91" s="1" t="inlineStr">
+      <c r="T91" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="T91" s="1" t="inlineStr">
+      <c r="U91" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="U91" s="1" t="inlineStr">
+      <c r="V91" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="V91" s="1" t="inlineStr">
+      <c r="W91" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="W91" s="1" t="inlineStr">
+      <c r="X91" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="X91" s="1" t="inlineStr">
+      <c r="Y91" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Y91" s="1" t="inlineStr">
+      <c r="Z91" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Z91" s="1" t="inlineStr">
+      <c r="AA91" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AA91" s="1" t="inlineStr">
+      <c r="AB91" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AB91" s="1" t="inlineStr">
+      <c r="AC91" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AC91" s="1" t="inlineStr">
+      <c r="AD91" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -8020,42 +8106,42 @@
           <t>1 ,2 ,3 ,1 ,4 ,2 ,1 ,4 ,2 ,1</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr">
+      <c r="Q92" t="inlineStr">
         <is>
           <t>15,12,5,6,7,8,5,8,10,30</t>
         </is>
       </c>
-      <c r="Q92" t="inlineStr">
+      <c r="R92" t="inlineStr">
         <is>
           <t>106</t>
         </is>
       </c>
-      <c r="R92" t="inlineStr">
+      <c r="S92" t="inlineStr">
         <is>
           <t>15,12,5,6,7,8,5,8,10,30</t>
         </is>
       </c>
-      <c r="S92" t="inlineStr">
+      <c r="T92" t="inlineStr">
         <is>
           <t>hhmmlmhmLm</t>
         </is>
       </c>
-      <c r="T92" t="inlineStr">
+      <c r="U92" t="inlineStr">
         <is>
           <t>hhmmlmhmLm</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
+      <c r="AA92" t="inlineStr">
         <is>
           <t>8b2ab344-e968-4445-b403-e548e2f0db2d</t>
         </is>
       </c>
-      <c r="AA92" t="inlineStr">
+      <c r="AB92" t="inlineStr">
         <is>
           <t>8b2ab344-e968-4445-b403-e548e2f0db2d</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr">
+      <c r="AD92" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -8072,42 +8158,42 @@
           <t>1 ,2 ,3 ,2 ,1 ,2 ,1 ,4 ,2 ,1</t>
         </is>
       </c>
-      <c r="P93" t="inlineStr">
+      <c r="Q93" t="inlineStr">
         <is>
           <t>15,12,5,5,7,4,5,7,8,30</t>
         </is>
       </c>
-      <c r="Q93" t="inlineStr">
+      <c r="R93" t="inlineStr">
         <is>
           <t>98</t>
         </is>
       </c>
-      <c r="R93" t="inlineStr">
+      <c r="S93" t="inlineStr">
         <is>
           <t>15,12,5,5,7,4,5,7,8,30</t>
         </is>
       </c>
-      <c r="S93" t="inlineStr">
+      <c r="T93" t="inlineStr">
         <is>
           <t>hhmhmhhlmm</t>
         </is>
       </c>
-      <c r="T93" t="inlineStr">
+      <c r="U93" t="inlineStr">
         <is>
           <t>hhmhmhhlmm</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
+      <c r="AA93" t="inlineStr">
         <is>
           <t>9c058e2e-80b5-4da3-b171-a802077dec24</t>
         </is>
       </c>
-      <c r="AA93" t="inlineStr">
+      <c r="AB93" t="inlineStr">
         <is>
           <t>9c058e2e-80b5-4da3-b171-a802077dec24</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr">
+      <c r="AD93" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -8124,42 +8210,42 @@
           <t>1 ,2 ,3 ,1 ,2</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr">
+      <c r="Q94" t="inlineStr">
         <is>
           <t>15,12,5,6,30</t>
         </is>
       </c>
-      <c r="Q94" t="inlineStr">
+      <c r="R94" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="R94" t="inlineStr">
+      <c r="S94" t="inlineStr">
         <is>
           <t>15,12,5,6,30</t>
         </is>
       </c>
-      <c r="S94" t="inlineStr">
+      <c r="T94" t="inlineStr">
         <is>
           <t>hhmmm</t>
         </is>
       </c>
-      <c r="T94" t="inlineStr">
+      <c r="U94" t="inlineStr">
         <is>
           <t>hhmmm</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
+      <c r="AA94" t="inlineStr">
         <is>
           <t>e1a2f47f-32a9-46a1-bc65-d50cded77733</t>
         </is>
       </c>
-      <c r="AA94" t="inlineStr">
+      <c r="AB94" t="inlineStr">
         <is>
           <t>e1a2f47f-32a9-46a1-bc65-d50cded77733</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
+      <c r="AD94" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
